--- a/光伏配储项目/电价数据/2026/奎阁站.xlsx
+++ b/光伏配储项目/电价数据/2026/奎阁站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48208</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7555700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5399299999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.55521</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48327</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47413</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42393</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.42907</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12755</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03693</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.03221</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.20607</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.0323</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.06659999999999999</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.02612</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.14739</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.13678</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.07615000000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53749</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73407</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12306</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.19755</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6613600000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8656200000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47427</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19644</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.41283</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.2756</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.98648</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28217</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.4777</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43673</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68321</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.73342</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.08348</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89337</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8006</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76147</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48363</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46474</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42764</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71745</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.88993</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9431499999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50288</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5253099999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50984</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49181</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.43045</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.40861</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44794</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.16352</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.02397</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.08408</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.49314</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.49007</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50405</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.11197</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12223</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.50841</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.04197</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.02436</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>-0.03293</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>-0.02985</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.03493</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.78208</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.25623</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.13822</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.23085</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.21331</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.23885</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.5414600000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.59274</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74333</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7543300000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16158</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.25008</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13053</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8376399999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20538</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10627</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25644</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02214</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09049</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65152</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98339</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9142400000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.95763</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7795</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.88593</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7356699999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.78097</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7263200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.75946</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42987</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44527</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33494</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51332</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49337</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48992</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44477</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43174</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47795</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21543</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.04453</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.28213</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.18602</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7803600000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.46199</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.21824</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43024</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.50634</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.47088</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.4313</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28547</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6211599999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6462</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.46648</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5465099999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.48347</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61117</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61776</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.56933</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55728</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7161799999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6010700000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5176799999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.5514199999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34235</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5147999999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.50326</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43896</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43137</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.08037999999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.12294</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.03870000000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56104</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17372</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.15781</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.12025</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6243500000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44364</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40693</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47494</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.45006</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50979</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46714</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47491</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48545</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5486599999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55816</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46945</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5047900000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40641</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42239</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32139</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.08851000000000001</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26877</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.07476999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26668</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.15601</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.09386</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13163</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.08509</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04618999999999999</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.00808</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.15818</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.15752</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.03811</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.01414</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.00446</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01877</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24009</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48748</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.54901</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37277</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.86921</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.46458</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5787599999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.53703</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.55108</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.6243300000000001</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10214</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00504</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19672</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04454</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26142</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05087</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.04904</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34812</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32385</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43308</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7854800000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18704</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86922</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79095</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.54299</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20695</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.43228</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45661</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.45935</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45529</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42361</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6725399999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.50712</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62978</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.81987</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8844299999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.50118</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.67183</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.50156</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.05701</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.81225</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8752300000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.51958</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.9152400000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.84605</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5904700000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47974</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.48391</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.54522</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.48761</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37282</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93704</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.53223</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47869</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45953</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.55674</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.47264</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.47056</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.6198899999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.4465</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41816</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.21901</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.08751</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.26132</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26785</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20088</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25875</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.53886</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47545</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.47985</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4661</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4679700000000001</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.79337</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.43704</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9507000000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48443</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.2047</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.73162</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8236</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.68274</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.81533</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.60477</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47759</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.52866</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46621</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.50096</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44145</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.6204500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43653</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45888</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.48829</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45834</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.51858</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44607</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.52664</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43648</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43267</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.47214</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.51619</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47846</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.51854</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.46536</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.43279</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6347999999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.5726100000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25181</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01734</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26453</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25918</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.65713</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.55324</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.03102</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.5599299999999999</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.52642</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.51415</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.37241</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.52395</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.45717</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.41708</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.41959</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.43298</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.5540499999999999</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.52247</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.44865</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.5364500000000001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.06970999999999999</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.09762</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.11499</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.08209000000000001</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.08977</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26522</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.10107</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.22978</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.08522</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25635</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12589</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05102</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.02723</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.06293</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16046</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.07337</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45849</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.44284</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.5497000000000001</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.47063</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.4606</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.54865</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.5348099999999999</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.53063</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.53728</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4632</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.41131</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41143</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.39264</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.6868200000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.57202</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49871</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.48688</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.41697</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.43342</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44942</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44613</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.54792</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.43266</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26441</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23453</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17277</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21379</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19369</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>-0.04715999999999999</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.04046</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>-0.0287</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25781</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40729</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40616</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.5271699999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42155</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47619</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.44089</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39626</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.63916</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.64651</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.4217</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45508</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.13552</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67959</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5179600000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.47017</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46473</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.43794</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25944</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26328</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.17637</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.18628</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.25546</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.55479</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.12968</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43656</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.58212</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48203</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44901</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.72088</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.06757</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.9077799999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.73248</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5292899999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.68214</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.42867</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.40466</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.52086</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.43358</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.44784</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.47124</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.44037</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.48116</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.46332</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.44918</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.51156</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.46222</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.4729100000000001</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.42484</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36934</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.39457</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.60694</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.42584</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41817</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.49398</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41816</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.67564</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.09187</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.5266799999999999</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.55041</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.37544</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.40319</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.42626</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26073</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.10734</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.23394</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.19996</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.12426</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.22016</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.25275</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25138</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.2162</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.25786</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24798</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28075</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.47589</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.57076</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.51224</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47139</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.68174</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6579400000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.65385</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84954</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.6265299999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.21145</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.6790900000000001</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52543</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.4659700000000001</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.61077</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.50686</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.48808</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41778</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.39484</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.39094</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5955900000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.73376</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.6372000000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.48102</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.45786</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.47256</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.46576</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41439</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.46144</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.45881</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43855</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40777</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.4883</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.44436</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47521</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.48066</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.46978</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5631900000000001</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.55079</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.73788</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62899</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.54384</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.61785</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53984</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46522</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41474</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43083</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46863</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5482400000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45429</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.47351</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43293</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64746</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6170800000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.19347</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.43226</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.44073</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.47452</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.51137</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.60265</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.64242</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.6448200000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.7117899999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.9600299999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.19048</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.30824</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.9436</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.11494</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.92845</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.15861</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78912</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6426799999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69202</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.56624</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.5958300000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.59262</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.5805900000000001</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.57226</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.7014400000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.49899</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.52222</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5474600000000001</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45411</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.5322100000000001</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4357799999999999</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.45644</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.58092</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.47127</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.48032</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45347</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.43797</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.42054</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.62861</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.45983</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.41608</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40641</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.26336</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5181399999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.02272</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.02901</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44697</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.49367</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.47375</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45528</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43716</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.52604</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.49716</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.50835</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.5240900000000001</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.5012099999999999</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.46913</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.47868</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4746</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.5150800000000001</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.4891</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.53298</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.51342</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.47012</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.6297999999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.4821</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.49637</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.50269</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.46418</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.48587</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.47268</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.63346</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.60236</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.59635</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.47229</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.61048</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.44359</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.5710700000000001</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.44778</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.45919</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.45954</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.55565</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.55383</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.57064</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.49877</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.57064</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.17927</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.20764</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.20996</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.43724</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.22868</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.07183</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.26991</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.08656999999999999</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.10576</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18081</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22184</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27389</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21343</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.46277</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45414</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.47823</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.5019</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.47555</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.44673</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44255</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.43731</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50928</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.46811</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.42854</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.52337</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.51658</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.48836</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.5278999999999999</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.51879</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.51879</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.51247</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.51247</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.51625</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.51247</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.51309</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.5282100000000001</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.52776</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.53123</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03425</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00098</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15167</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02285</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01488</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04104</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02949</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03712</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01491</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03556</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20578</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.52389</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.54314</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.43077</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.41194</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.19887</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.02812</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.49633</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.88801</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52961</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.54414</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.59948</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.4537</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.5139600000000001</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.47519</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.48834</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.48271</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.64619</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.46924</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.6688999999999999</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.57889</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.66062</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.6043099999999999</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.66203</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.6298899999999999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.61156</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.63676</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.67908</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46637</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.54339</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41657</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.60238</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52578</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.52734</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.42314</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.91192</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8735499999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.0454</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>-0.03649</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.03612</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.04624</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.04926</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.00488</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.45028</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.45181</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.0528</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.16586</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.12305</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.00115</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.15143</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.0538</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.15832</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.86368</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.86194</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8660599999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.96288</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.15408</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.1543</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.14812</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.42391</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.60888</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.90138</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.4921</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.84658</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.51967</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.62849</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.52351</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.49009</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.5359700000000001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.43226</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6718999999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.45052</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.47684</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.44057</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.46381</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.46908</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.62997</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.5423300000000001</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.51217</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.50961</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62053</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.67822</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.52783</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.01037</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.15841</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.26987</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.23396</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.21496</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.43082</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41531</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.6344</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.2588</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5102599999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.9229700000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.61738</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.55123</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.54196</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.49159</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.68141</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.41009</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42835</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.41466</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.40513</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.51724</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.4869</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.48108</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40936</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.55226</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43909</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.86609</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.01957</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.8464400000000001</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.78535</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.60427</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.41037</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.0177</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.83263</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58447</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55788</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.66023</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.81679</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5758799999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.93004</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.8150499999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.61588</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.6186900000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43908</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.46872</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.5452</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.54296</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.45107</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.45052</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.28386</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40913</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.4042</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.53198</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44439</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.45333</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.44024</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42891</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.46328</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.4246</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41184</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44606</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45565</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.52274</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6664</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.71209</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.78892</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.54828</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.43531</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.78244</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4852</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.62088</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9520599999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.54915</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.53195</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5462100000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.02231</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.48396</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49741</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.44034</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40575</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40868</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40848</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.46036</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.6227999999999999</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.42205</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.44756</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17743</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17448</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20782</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09866</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.18528</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01484</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05691</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26499</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.00839</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02953</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04259</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11108</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02686</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00215</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23284</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.18337</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20841</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5475399999999999</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44096</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.4603</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.52154</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47523</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43869</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41273</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44778</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.48216</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.42065</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.26864</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.23219</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42626</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.41171</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.40575</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40569</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26705</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.13325</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.2724</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.43336</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.43582</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.44311</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41638</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.42231</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.42024</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38988</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48467</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.45683</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40778</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17691</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14654</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19979</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02295</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24212</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03409</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04752</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.02191</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22231</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14795</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26425</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25912</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.43118</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42134</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.51134</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41796</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40912</v>
       </c>
     </row>
   </sheetData>
